--- a/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU03-LU04/LU03-LU04_천부-협백_해부생리_통합분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU03-LU04/LU03-LU04_천부-협백_해부생리_통합분석데이터.xlsx
@@ -26,6 +26,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LayerA_papers" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외부검색로그" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMA_해부실체" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1938,7 +1939,6 @@
         <v/>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -2048,7 +2048,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -5196,7 +5195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5566,6 +5565,240 @@
           <t>3</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LU3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:08</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>200</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>("LU3" OR "Tianfu" OR "天府") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("LU3" OR "Tianfu" OR "天府") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LU3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:08</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>200</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Tianfu" OR "LU3" | doi_starts_with:10.13702,title_and_abstract.search:"Tianfu" OR "LU3" | has_doi:true,title_and_abstract.search:"Tianfu" OR "LU3" AND (acupuncture OR electroacupuncture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LU3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:08</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>200</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Tianfu acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LU3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:08</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>24</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LU4</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:22</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pubmed</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>("LU4" OR "Xiabai" OR "侠白") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("LU4" OR "Xiabai" OR "侠白") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LU4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:22</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>200</v>
+      </c>
+      <c r="E15" t="n">
+        <v>9</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>doi_starts_with:10.13703,title_and_abstract.search:"Xiabai" OR "LU4" | doi_starts_with:10.13702,title_and_abstract.search:"Xiabai" OR "LU4" | has_doi:true,title_and_abstract.search:"Xiabai" OR "LU4" AND (acupuncture OR electroacupuncture)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LU4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>crossref</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>200</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Xiabai acupuncture nerve reflex</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LU4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:44:22</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>14</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5578,7 +5811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6018,6 +6251,28 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>pack_LU3.md·pack_LU4.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FMA_해부실체 시트 신설 (2026-10-23)</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 실체 ID·지배신경·줄기·분절·교재 비교 추가(LU03·LU04). 4개 Target ARI·B-Check 불변</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>fma_query.py profile LU03/LU04; 보고서 4·6·8절·부록 A</t>
         </is>
       </c>
     </row>
@@ -6140,6 +6395,1342 @@
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>명실고: "本穴定位，古今不同". 1판 《讲义》의 "重按有動脈應手"에 대해 "按如今之定位，無論如何重按，也不會觸及動脈搏動". "侠白部位在動脈中，故該穴仍可能由手太陰標脈'天府脈'演變而來". 주치 "心痛" = 胸痹心痛 계열</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>경혈</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>교재 용어</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FMA_ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>FMA_label</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>대응 수준</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>출처 교재</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>지배신경(FMA nerve_supply)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>상위 줄기(FMA)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>척수 분절(FMA segmental_supply)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>위팔두갈래근 (biceps brachii)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>37670</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Biceps brachii</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>C5(segmental), C6(segmental)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>어깨세모근 (deltoid)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>32521</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Deltoid</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FMA:65300 Deltoid branch of posterior branch of axillary nerve; FMA:81322 Deltoid branch of anterior branch of axillary nerve</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Posterior branch of axillary nerve → Axillary nerve</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>C5(primary/segmental), C6(secondary/segmental)</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>위팔두갈래근의 긴갈래 (long head of the biceps brachii)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>37683</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Long head of biceps brachii</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FMA:81239 Branch of musculocutaneous nerve to long head of biceps brachii</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>위팔두갈래근 전체(37670)의 부분 — 같은 근육</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>큰가슴근 (pectoralis major)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9627</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Pectoralis major</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FMA:81260 Branch of medial pectoral nerve to clavicular part of pectoralis major; FMA:81333 Branch of medial pectoral nerve to sternocostal part of pectoralis major</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Medial pectoral nerve</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>아래가쪽위팔피부신경 (inferior lateral brachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inferior lateral cutaneous nerve of arm</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>FMA:288541 Peripheral segment of radial nerve</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>가쪽아래팔피부신경 (lateral antebrachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>39080</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Lateral cutaneous nerve of forearm</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>FMA:288511 Peripheral segment of musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>정중신경 (median nerve)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>14385</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Median nerve</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>근육피부신경 (musculocutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>37064</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>뒤아래팔피부신경 (posterior antebrachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>39145</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Posterior cutaneous nerve of forearm</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FMA:288541 Peripheral segment of radial nerve</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>위가쪽위팔피부신경 (superior lateral cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>65303</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Superior lateral cutaneous nerve of arm</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>수동 대응</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>자동 대응 실패(교재 표기 'of arm' 누락)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>등쪽 아래팔 피부신경 (dorsal antebrachial cutaneous n., C5-6)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>FMA:39145 Posterior cutaneous nerve of forearm과 같은 구조로 판단(중복 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>위팔동ㆍ정맥 (brachial artery and vein)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>22689</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Brachial artery</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>FMA is_a Segment of subclavian artery(모델링)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>위팔동ㆍ정맥 (brachial artery and vein)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>22934</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Brachial vein</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>FMA:13329 Axillary vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>노쪽피부정맥 (cephalic vein)</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13324</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Cephalic vein</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LU03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>C5, C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>위팔두갈래근 (biceps brachii)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>37670</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Biceps brachii</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>C5(segmental), C6(segmental)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>근육</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>위팔두갈래근의 긴갈래 (long head of the biceps brachii)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>37683</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Long head of biceps brachii</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>FMA:81239 Branch of musculocutaneous nerve to long head of biceps brachii</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>위팔두갈래근 전체(37670)의 부분 — 같은 근육</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>아래가쪽위팔피부신경 (inferior lateral brachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>44949</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Inferior lateral cutaneous nerve of arm</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>FMA:288541 Peripheral segment of radial nerve</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>가쪽아래팔피부신경 (lateral antebrachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>39080</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Lateral cutaneous nerve of forearm</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>FMA:288511 Peripheral segment of musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>정중신경 (median nerve)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>14385</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Median nerve</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>근육피부신경 (musculocutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>37064</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Musculocutaneous nerve</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>뒤아래팔피부신경 (posterior antebrachial cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>39145</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Posterior cutaneous nerve of forearm</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>FMA:288541 Peripheral segment of radial nerve</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>위가쪽위팔피부신경 (superior lateral cutaneous nerve)</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>65303</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Superior lateral cutaneous nerve of arm</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>수동 대응</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>자동 대응 실패(교재 표기 'of arm' 누락)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>신경</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>등쪽 아래팔 피부신경 (dorsal antebrachial cutaneous n., C5-6)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>김재효</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>FMA:39145 Posterior cutaneous nerve of forearm과 같은 구조로 판단(중복 표기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>위팔동ㆍ정맥 (brachial artery and vein)</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>22689</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Brachial artery</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>FMA is_a Segment of subclavian artery(모델링)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>위팔동ㆍ정맥 (brachial artery and vein)</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>22934</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Brachial vein</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>공통교재</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>FMA:13329 Axillary vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>혈관</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>노쪽피부정맥 (cephalic vein)</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13324</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cephalic vein</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>공통교재·김재효</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>FMA 미기재</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>LU04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>분절 합집합</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C5, C6</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>출처</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FMA 5.1.0 로컬 색인, fma_query.py profile LU03/LU04 (2026-10-23). B1 보조(등록부 미등재)</t>
         </is>
       </c>
     </row>
@@ -6699,7 +8290,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
@@ -7421,7 +9011,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>

--- a/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU03-LU04/LU03-LU04_천부-협백_해부생리_통합분석데이터.xlsx
+++ b/01_경혈별_해부생리_분석보고서/LU_수태음폐경/LU03-LU04/LU03-LU04_천부-협백_해부생리_통합분석데이터.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_3D좌표_Layer" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_자침심도" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_교재비교" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_분기추론_쟁점" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_분기추론_TriTarget" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_생의학근거" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_주치분리" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구판_10_ARI평가" sheetId="11" state="visible" r:id="rId11"/>
@@ -57,7 +57,7 @@
       <color rgb="009C5700"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -101,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -113,6 +118,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2019,11 +2033,11 @@
         <v>6.2</v>
       </c>
       <c r="D3">
-        <f>SQRT(B2^2+C2^2)</f>
+        <f>SQRT(B3^2+C3^2)</f>
         <v/>
       </c>
       <c r="E3">
-        <f>IF(D2&gt;15,"이원 분기","단일")</f>
+        <f>IF(D3&gt;10,"분기(Target 1≡2 vs Target 3)","단일")</f>
         <v/>
       </c>
     </row>
@@ -2040,11 +2054,11 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <f>SQRT(B3^2+C3^2)</f>
+        <f>SQRT(B4^2+C4^2)</f>
         <v/>
       </c>
       <c r="E4">
-        <f>IF(D3&gt;15,"이원 분기","단일")</f>
+        <f>IF(D4&gt;10,"분기(Target 1≡2 vs Target 3)","단일")</f>
         <v/>
       </c>
     </row>
@@ -2088,11 +2102,11 @@
         <v>4</v>
       </c>
       <c r="D7">
-        <f>B6*2.3</f>
+        <f>B7*2.3</f>
         <v/>
       </c>
       <c r="E7">
-        <f>C6*2.3</f>
+        <f>C7*2.3</f>
         <v/>
       </c>
     </row>
@@ -2109,11 +2123,11 @@
         <v>4</v>
       </c>
       <c r="D8">
-        <f>B7*2.3</f>
+        <f>B8*2.3</f>
         <v/>
       </c>
       <c r="E8">
-        <f>C7*2.3</f>
+        <f>C8*2.3</f>
         <v/>
       </c>
     </row>
@@ -2130,11 +2144,11 @@
         <v>3</v>
       </c>
       <c r="D9">
-        <f>B8*2.3</f>
+        <f>B9*2.3</f>
         <v/>
       </c>
       <c r="E9">
-        <f>C8*2.3</f>
+        <f>C9*2.3</f>
         <v/>
       </c>
     </row>
@@ -2151,11 +2165,11 @@
         <v>5</v>
       </c>
       <c r="D10">
-        <f>B9*2.3</f>
+        <f>B10*2.3</f>
         <v/>
       </c>
       <c r="E10">
-        <f>C9*2.3</f>
+        <f>C10*2.3</f>
         <v/>
       </c>
     </row>
@@ -2172,11 +2186,11 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <f>B10*2.3</f>
+        <f>B11*2.3</f>
         <v/>
       </c>
       <c r="E11">
-        <f>C10*2.3</f>
+        <f>C11*2.3</f>
         <v/>
       </c>
     </row>
@@ -2191,7 +2205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2426,7 +2440,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S_orig④通考교감</t>
+          <t>S_orig④通考·经络通鉴교감</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2438,6 +2452,11 @@
       <c r="E9" t="n">
         <v>87.5</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-25 经络通鉴 재확인: 단계 불변</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2760,7 +2779,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S_orig④通考교감</t>
+          <t>S_orig④通考·经络通鉴교감</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -2772,6 +2791,11 @@
       <c r="E24" t="n">
         <v>100</v>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-10-25 经络通鉴 재확인: 단계 불변</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3094,7 +3118,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S_orig④通考교감</t>
+          <t>S_orig④通考·经络通鉴교감</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -3106,6 +3130,11 @@
       <c r="E39" t="n">
         <v>62.5</v>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-10-25 经络通鉴 재확인: 단계 불변</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3428,7 +3457,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>S_orig④通考교감</t>
+          <t>S_orig④通考·经络通鉴교감</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -3440,6 +3469,11 @@
       <c r="E54" t="n">
         <v>62.5</v>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-10-25 经络通鉴 재확인: 단계 불변</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3595,7 +3629,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>cLU3 우위 선언</t>
+          <t>cLU3 우위 선언(Target 1≡2 &gt; Target 3, Tri-Target 규칙)</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3661,39 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>cLU4 우위 선언</t>
+          <t>cLU4 우위 선언(Target 1≡2 &gt; Target 3, Tri-Target 규칙)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Tri-Target 대응</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>cLU3·cLU4 = Target 1≡2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>pLU3·pLU4 = Target 3</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>분기 기준 Δ &gt; 10mm</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Δ ≈ 28~29mm(모델)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ARI 불변</t>
         </is>
       </c>
     </row>
@@ -5588,8 +5654,6 @@
       <c r="E10" t="n">
         <v>13</v>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>("LU3" OR "Tianfu" OR "天府") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("LU3" OR "Tianfu" OR "天府") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
@@ -5618,8 +5682,6 @@
       <c r="E11" t="n">
         <v>11</v>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>doi_starts_with:10.13703,title_and_abstract.search:"Tianfu" OR "LU3" | doi_starts_with:10.13702,title_and_abstract.search:"Tianfu" OR "LU3" | has_doi:true,title_and_abstract.search:"Tianfu" OR "LU3" AND (acupuncture OR electroacupuncture)</t>
@@ -5648,8 +5710,6 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>Tianfu acupuncture nerve reflex</t>
@@ -5681,7 +5741,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5705,8 +5764,6 @@
       <c r="E14" t="n">
         <v>5</v>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>("LU4" OR "Xiabai" OR "侠白") AND (acupuncture OR electroacupuncture) AND (nerve OR reflex OR autonomic OR mechanism OR anatomy) | ("LU4" OR "Xiabai" OR "侠白") AND ("Zhongguo Zhen Jiu"[Journal] OR "Zhen Ci Yan Jiu"[Journal])</t>
@@ -5735,8 +5792,6 @@
       <c r="E15" t="n">
         <v>9</v>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>doi_starts_with:10.13703,title_and_abstract.search:"Xiabai" OR "LU4" | doi_starts_with:10.13702,title_and_abstract.search:"Xiabai" OR "LU4" | has_doi:true,title_and_abstract.search:"Xiabai" OR "LU4" AND (acupuncture OR electroacupuncture)</t>
@@ -5765,8 +5820,6 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>Xiabai acupuncture nerve reflex</t>
@@ -5798,7 +5851,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5811,7 +5863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6273,6 +6325,50 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>fma_query.py profile LU03/LU04; 보고서 4·6·8절·부록 A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-25 Framework 2.7.7 (md 머리말·§0·§1·§2·§3·§4·§6·§7·§8·§10, xlsx)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>3대 원전, Dual-Target(Target 1 cLU / Target 2 pLU, Δ &gt; 15mm), ④ 通考 교감</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>4대 원전(经络通鉴 행·Rank 4 교감), 证治通鉴 한글 번역본 병기, 자입 기준점(안쪽 위팔두갈래근고랑 위팔동맥), Tri-Target 10mm 기준 Target 1≡2(cLU) vs Target 3(pLU), ④ 재확인 불변, ARI 불변; 시트 07_분기추론_쟁점 → 07_분기추론_TriTarget 재작성, 01·04·13·ARI_v3.0 표기 갱신; 13_Δ 시트 수식의 행 참조 1칸 어긋남(경고 행 삽입 후 남은 오류: D3=SQRT(B2…) 등) 바로잡음, 분기 수식 기준 &gt;15 → &gt;10</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>프레임워크 2.7.7; 분기 기준 Δ &gt; 10mm(2026-10-25 개정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-25 Target 제외 규칙 (md §3)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>窦太师 "肘腕上五寸"·"天府下二寸" 변이를 혼동 사례로만 기술</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>Rank 5 Target 제외 규칙(후대 이설·환산 척도 이문)으로 Target 미설정 명시; Target 구성·ARI 불변</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>프레임워크 Rank 5 Target 제외 규칙(2026-10-25)</t>
         </is>
       </c>
     </row>
@@ -6287,7 +6383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.90000000000001" customWidth="1" min="1" max="1"/>
@@ -6306,7 +6402,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>1. 문헌 스크리닝 표 (Rank 1·2: 핵심 3대 원전 직접 대조)</t>
+          <t>1. 문헌 스크리닝 표 (Rank 1·2: 핵심 4대 원전 직접 대조 — 2026-10-25 《中国针灸经络通鉴》 행·证治通鉴 번역본 포인터 추가)</t>
         </is>
       </c>
     </row>
@@ -6395,6 +6491,182 @@
       <c r="D6" s="3" t="inlineStr">
         <is>
           <t>명실고: "本穴定位，古今不同". 1판 《讲义》의 "重按有動脈應手"에 대해 "按如今之定位，無論如何重按，也不會觸及動脈搏動". "侠白部位在動脈中，故該穴仍可能由手太陰標脈'天府脈'演變而來". 주치 "心痛" = 胸痹心痛 계열</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 맥명·표맥</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L351·L355·L357·L393·L401</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>"腋内动脉，手太阴也，名曰天府"(本输) / "腋下动脉，臂太阴也，名曰天府"(寒热病); 해설: 진단 맥동처이자 경맥 標, 天府는 《卫气》에서도 수태음의 標</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>— (天府 표맥에서 侠白 유래 가능성은 通考 해석)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 백서 교주</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_05_第壹编_第三篇_经络专篇研究.md L1124·L1140</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>《足臂》 "出腋内廉" = 天府 표맥, 《阴阳》 "出臂内阴" = 天府 동맥</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 明堂 조문</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_01_第壹编_第一篇_“经脉”概念的形成与经络学说的建立.md L419·L423</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>"天府：在腋下三寸臂臑内廉动脉，手太阴脉气所发" + 杨上善 주</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>"侠白：在天府下去肘五寸动脉" + 杨上善 주 "手太阴脉动此穴也"</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 맥동처</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_15_第贰编_第六篇_经络病候与诊法(二).md L299; 中国针灸经络通鉴_17_第叁编_第一篇_手太阴经脉、经别、络脉和经筋.md L122</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>杨注 三部九候 中部之天 "动在中府、天府、侠白、尺泽四处"; "手太阴动于太渊，又动于尺泽、侠白、天府"</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>같음(侠白 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 순행·归经</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_17_第叁编_第一篇_手太阴经脉、经别、络脉和经筋.md L241·L343·L415; 中国针灸经络通鉴_05_第壹编_第三篇_经络专篇研究.md L1166</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>《医学纲目》 주 "臑内廉凡有三脉，太阴居前"; 안어 L343 순행 방향·장부 분기만(노쪽 이동 언급 없음); 明堂 肘膝以下만 归经</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>같음</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 오기</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>中国针灸经络通鉴_26_第叁编_第九篇_手厥阴经脉、经别、络脉和经筋.md L295</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>《医心方》 卷二十二 그림 "天府" → "天泉" 오기</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸经络通鉴》 미언급</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>전 39편 grep: 天府·侠白·俠白·夹白·挟白·白雄</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>가쪽 이동 경위 직접 언급 없음</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>白雄 이명·가쪽 정위 언급 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>《中国针灸证治通鉴》 번역본 대조</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>中国针灸证治通鉴_24_第叁编_五官病证_鼻病_口齿病_喉痹咽痛.md L10·L46·L218 / _한글번역.md L12·L72·L372; 中国针灸证治通鉴_26_第叁编_外科病证_痔漏至虫兽咬伤.md L366·L368·L436·L490 / _한글번역.md L565·L567·L643·L717</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>鼻衄·瘿 원문과 한글 번역 병기(보고서 §1)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>赤白汗斑(출전 《古今医统大全·经验秘方》 卷九十三)·白癜风 원문과 한글 번역 병기</t>
         </is>
       </c>
     </row>
@@ -6516,14 +6788,11 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>C5(segmental), C6(segmental)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6574,7 +6843,6 @@
           <t>C5(primary/segmental), C6(secondary/segmental)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -6680,7 +6948,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -6716,7 +6983,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>FMA:288541 Peripheral segment of radial nerve</t>
@@ -6727,7 +6993,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -6763,7 +7028,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>FMA:288511 Peripheral segment of musculocutaneous nerve</t>
@@ -6774,7 +7038,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6810,14 +7073,11 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6853,14 +7113,11 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6896,7 +7153,6 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>FMA:288541 Peripheral segment of radial nerve</t>
@@ -6907,7 +7163,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6943,8 +7198,6 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
@@ -6982,8 +7235,6 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
@@ -7029,8 +7280,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
@@ -7076,7 +7325,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>FMA:13329 Axillary vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
@@ -7087,7 +7335,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -7123,7 +7370,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
@@ -7134,7 +7380,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -7187,14 +7432,11 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>C5(segmental), C6(segmental)</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7285,7 +7527,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>FMA:288541 Peripheral segment of radial nerve</t>
@@ -7296,7 +7537,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7332,7 +7572,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>FMA:288511 Peripheral segment of musculocutaneous nerve</t>
@@ -7343,7 +7582,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -7379,14 +7617,11 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -7422,14 +7657,11 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -7465,7 +7697,6 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>FMA:288541 Peripheral segment of radial nerve</t>
@@ -7476,7 +7707,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -7512,8 +7742,6 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
@@ -7551,8 +7779,6 @@
           <t>김재효</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
@@ -7598,8 +7824,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>FMA 미기재</t>
@@ -7645,7 +7869,6 @@
           <t>공통교재</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>FMA:13329 Axillary vein → FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
@@ -7656,7 +7879,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7692,7 +7914,6 @@
           <t>공통교재·김재효</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>FMA:4725 Subclavian vein → FMA:4723 Brachiocephalic vein</t>
@@ -7703,7 +7924,6 @@
           <t>FMA 미기재</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -8196,12 +8416,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Target 1: 고전 동맥점 (cLU3 / cLU4)</t>
+          <t>Target 1≡2: 고전 문헌 위치 ≡ 촉진 실체화 위치 (cLU3 / cLU4)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Target 2: WHO 정위 (pLU3 / pLU4)</t>
+          <t>Target 3: WHO 위치 (pLU3 / pLU4)</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8501,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Δ &gt; 15mm → 이원 분기 확정</t>
+          <t>Δ &gt; 10mm → 분기 (Target 1≡2 vs Target 3) (2026-10-25 기준 개정, 판정 불변)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -8305,12 +8525,12 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Target 1: cLU3 / cLU4 (안쪽 동맥점)</t>
+          <t>Target 1≡2: cLU3 / cLU4 (안쪽 동맥점)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Target 2: pLU3 / pLU4 (가쪽 모서리)</t>
+          <t>Target 3: pLU3 / pLU4 (가쪽 모서리)</t>
         </is>
       </c>
     </row>
@@ -8778,138 +8998,449 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="66" customWidth="1" min="2" max="2"/>
-    <col width="66" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>⚠ 구판 v2.6 데이터 시트 — 원전 대조·채점 오류가 포함되어 있을 수 있음. 2026-10-04 v2.7 개정본 .md 보고서와 'ARI_v3.0'·'B-Check'·'개정이력' 시트가 정본.</t>
-        </is>
-      </c>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>7. 공간 변위 분기 추론 (Tri-Target, 분기 기준 Δ &gt; 10mm, 2026-10-25 개정)</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>7. 공간 변위 분기 추론 (Dual-Target Bifurcation)</t>
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>정의</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>천부(LU3)</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>협백(LU4)</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>대응·판정</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Target 1 고전 문헌 위치</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>《甲乙》·《明堂》 최초 기술</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>"腋下三寸，臂臑內廉動脈中"</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>"在天府下，去肘五寸動脈中"</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Target 2와 병합 → Target 1≡2 (cLU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Target 2 촉진 실체화 위치(자입 기준점)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>"動脈中" → 안쪽 위팔두갈래근고랑(FMA:74569) 위팔동맥(FMA:22689) 박동 위; 경계 위팔두갈래근(FMA:37670)·부리위팔근(FMA:37664, LU3)·위팔근(FMA:37667, LU4)·안쪽 근육사이막(FMA:37886)</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>X −14.5, Y 69, Z 18.2 (모델 cLU3)</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>X −13.2, Y 92, Z 17.5 (모델 cLU4)</t>
+        </is>
+      </c>
+      <c r="E4" s="7">
+        <f> Target 1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Target 3 WHO 위치</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>WHO 2008 lateral border of biceps brachii</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>X +13.8, Y 69, Z 12.0 (모델 pLU3)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>X +14.5, Y 92, Z 11.5 (모델 pLU4)</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>독립 분기 (pLU)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n"/>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Δ 산출 근거</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>천부 Δ (추정)</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>협백 Δ (추정)</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>판정 (10mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>T1–T2</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>최초 기술 자체가 "動脈中"으로 위치 지정</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>≈ 0~5mm</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>≈ 0~5mm</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>병합</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>T1–T3</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>√(ΔX²+ΔZ²), 모델 좌표</t>
+        </is>
+      </c>
+      <c r="C9" s="7">
+        <f>ROUND(SQRT(28.3^2+6.2^2),1)</f>
+        <v/>
+      </c>
+      <c r="D9" s="7">
+        <f>ROUND(SQRT(27.7^2+6^2),1)</f>
+        <v/>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>T2–T3</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>모델 cLU 좌표 = 동맥점</t>
+        </is>
+      </c>
+      <c r="C10" s="7">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="7">
+        <f>D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>분기</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>결론</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Target 1≡2 vs Target 3</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>10mm·15mm 기준 모두 같은 판정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="n"/>
+      <c r="B12" s="7" t="n"/>
+      <c r="C12" s="7" t="n"/>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>구판 대응</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>구 Target 1(고전 동맥점, cLU3·cLU4) → Target 1≡2</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>구 Target 2(WHO 정위, pLU3·pLU4) → Target 3</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>위치 불변 → 이중 채점 승계</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Tri-Target 판정</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>cLU3 vs pLU3 ΔARI 15.0, 구간 비중첩</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>cLU4 vs pLU4 ΔARI 18.7, 구간 비중첩</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>Target 1≡2 단독 우위(독립 Target 둘)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>쟁점 (구판 표 유지, 표기 갱신)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>쟁점</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>송석모(2022)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>황룡상 《针灸腧穴通考》</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>본 보고서 판정</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="E17" s="9" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>고전 천부·협백의 실체</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>위팔동맥 박동점(안쪽)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>위팔동맥 박동점(안쪽). 오늘날 수소음경 부위에 해당</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>일치. 확정</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="E18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>《灵枢·经脉》 "下循臑內"</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>위팔 안쪽 = 위팔동맥 노선</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>帛書보다 노쪽으로 이동한 단계 ("已較…移向上臂橈側"). 혈위 정위는 이를 늦게 따라감</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>해석 분기. "行少陰心主之前"이 노쪽 이동을 시사한다는 황룡상의 견해를 배제할 수 없음</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="E19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>가쪽으로 바뀐 경위</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>20세기 중반 이후. 동맥 기재가 빠지고 간편취혈법(팔을 들어 코끝이 닿는 곳)의 모호성 때문에 오인했다는 추정</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>明正统铜人이 이미 굽힘면 노쪽에 표시. 해부학 용어로 "외측연"을 처음 쓴 것은 일본 침구서. 중국 교재는 4판부터</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>다원적 경위. 기존 비교보고서의 "1950년대 비묵인비 자세 오인" 단일 원인설은 두 출처 모두 그렇게 단정하지 않으므로 수정함</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="E20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>처방</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>WHO 위치를 오류로 보고 안쪽 동맥점으로 복원</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>현대 위치를 인정하고 주치·자법·층차해부를 새 위치에 맞게 고침 (天府는 비부·상완 국소 위주, 폐 증상은 부차적으로)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>이원 타깃 병존: 고전 주치는 cLU에, 국소 주치는 pLU에 귀속. 표준 개정 여부는 학계 판단 사항으로 남김</t>
-        </is>
-      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>Target 1≡2·Target 3 병존: 고전 주치는 cLU에, 국소 주치는 pLU에 귀속. 표준 개정 여부는 학계 판단 사항으로 남김</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
